--- a/test-data/PythonTest_Input_Scenario2.xlsx
+++ b/test-data/PythonTest_Input_Scenario2.xlsx
@@ -1,188 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Scenario"/>
-    <sheet r:id="rId2" sheetId="2" name="login2"/>
-    <sheet r:id="rId3" sheetId="3" name="login"/>
-    <sheet r:id="rId4" sheetId="4" name="homepage"/>
-    <sheet r:id="rId5" sheetId="5" name="listview"/>
-    <sheet r:id="rId6" sheetId="6" name="ptpfollowup"/>
-    <sheet r:id="rId7" sheetId="7" name="MenuPage"/>
-    <sheet r:id="rId8" sheetId="8" name="rcfollowup"/>
-    <sheet r:id="rId9" sheetId="9" name="deliquent_reason"/>
+    <sheet name="Scenario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="login2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="login" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="homepage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="listview" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ptpfollowup" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MenuPage" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="rcfollowup" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="deliquent_reason" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
-  <si>
-    <t>ReasonType</t>
-  </si>
-  <si>
-    <t>ReasonCode</t>
-  </si>
-  <si>
-    <t>ReasonDescription</t>
-  </si>
-  <si>
-    <t>Delinquent Reason</t>
-  </si>
-  <si>
-    <t>TST01</t>
-  </si>
-  <si>
-    <t>Automation Test Reason 1</t>
-  </si>
-  <si>
-    <t>TST02</t>
-  </si>
-  <si>
-    <t>Automation Test Reason 2</t>
-  </si>
-  <si>
-    <t>Result Code</t>
-  </si>
-  <si>
-    <t>TC</t>
-  </si>
-  <si>
-    <t>MenuName</t>
-  </si>
-  <si>
-    <t>Portfolio Master</t>
-  </si>
-  <si>
-    <t>List View</t>
-  </si>
-  <si>
-    <t>Demo View</t>
-  </si>
-  <si>
-    <t>Reason Master</t>
-  </si>
-  <si>
-    <t>PTP</t>
-  </si>
-  <si>
-    <t>AccountNo</t>
-  </si>
-  <si>
-    <t>KB0000001002</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>Tenant</t>
-  </si>
-  <si>
-    <t>UserName</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>KBANK</t>
-  </si>
-  <si>
-    <t>ADMIN</t>
-  </si>
-  <si>
-    <t>Indus@123</t>
-  </si>
-  <si>
-    <t>StepCode</t>
-  </si>
-  <si>
-    <t>InputSheet</t>
-  </si>
-  <si>
-    <t>Login</t>
-  </si>
-  <si>
-    <t>/login2</t>
-  </si>
-  <si>
-    <t>Home Page</t>
-  </si>
-  <si>
-    <t>/homepage</t>
-  </si>
-  <si>
-    <t>Menu</t>
-  </si>
-  <si>
-    <t>/MenuPage</t>
-  </si>
-  <si>
-    <t>List view</t>
-  </si>
-  <si>
-    <t>/listview</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Collection -&gt; Followup</t>
-  </si>
-  <si>
-    <t>FollowUp</t>
-  </si>
-  <si>
-    <t>/ptpfollowup</t>
-  </si>
-  <si>
-    <t>/rcfollowup</t>
-  </si>
-  <si>
-    <t>/deliquent_reason</t>
-  </si>
-  <si>
-    <t>Logout</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFffffff"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFffffff"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0000ff"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF0000ff"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -221,39 +87,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,94 +469,133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="30.005" customWidth="1" bestFit="1"/>
+    <col width="20.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="30.005" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="2"/>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>StepCode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>InputSheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>/login2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Home Page</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>/homepage</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>/MenuPage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>List view</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>/listview</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Collection -&gt; Followup</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FollowUp</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>/ptpfollowup</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FollowUp</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>/rcfollowup</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reason Master</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>/deliquent_reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20.25" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -636,38 +603,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="16.005" customWidth="1" bestFit="1"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.005" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.005" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>25</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tenant</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>UserName</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KBANK</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Indus@123</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -676,37 +656,48 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="16.005" customWidth="1" bestFit="1"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.005" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.005" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="6">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tenant</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>UserName</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KBANK</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
         <v>1234</v>
       </c>
     </row>
@@ -716,24 +707,29 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="30.005" customWidth="1" bestFit="1"/>
+    <col width="30.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -742,24 +738,29 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="24.005" customWidth="1" bestFit="1"/>
+    <col width="24.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>17</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AccountNo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KB0000001002</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -768,24 +769,29 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="18.005" customWidth="1" bestFit="1"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Result Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PTP</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -794,39 +800,50 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="24.005" customWidth="1" bestFit="1"/>
+    <col width="24.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MenuName</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Master</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>List View</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Demo View</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Reason Master</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -835,24 +852,29 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="18.005" customWidth="1" bestFit="1"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Result Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -861,49 +883,68 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="34.005" customWidth="1" bestFit="1"/>
+    <col width="20.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ReasonType</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ReasonCode</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ReasonDescription</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Delinquent Reason</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>TST01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Automation Test Reason 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Delinquent Reason</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TST02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Automation Test Reason 2</t>
+        </is>
       </c>
     </row>
   </sheetData>
